--- a/data/locators.xlsx
+++ b/data/locators.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="29">
   <si>
     <t>PageName</t>
   </si>
@@ -43,7 +43,7 @@
     <t>id</t>
   </si>
   <si>
-    <t>user_input</t>
+    <t>user-name</t>
   </si>
   <si>
     <t/>
@@ -52,31 +52,19 @@
     <t>password</t>
   </si>
   <si>
-    <t>password_input</t>
-  </si>
-  <si>
     <t>loginBtn</t>
   </si>
   <si>
-    <t>xpath</t>
-  </si>
-  <si>
-    <t>//button[@type='submit']</t>
-  </si>
-  <si>
-    <t>rememberMe</t>
+    <t>login-button</t>
+  </si>
+  <si>
+    <t>errorMessage</t>
   </si>
   <si>
     <t>css</t>
   </si>
   <si>
-    <t>input[type='checkbox']</t>
-  </si>
-  <si>
-    <t>errorMessage</t>
-  </si>
-  <si>
-    <t>.error-message</t>
+    <t>.error-message-container</t>
   </si>
   <si>
     <t>DashboardPage</t>
@@ -85,52 +73,31 @@
     <t>dashboardHeader</t>
   </si>
   <si>
-    <t>//h1[text()='Dashboard']</t>
+    <t>.inventory_container</t>
   </si>
   <si>
     <t>userMenuBtn</t>
   </si>
   <si>
-    <t>.user-menu-btn</t>
+    <t>react-burger-menu-btn</t>
   </si>
   <si>
     <t>logoutBtn</t>
   </si>
   <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>Logout</t>
+    <t>logout_sidebar_link</t>
   </si>
   <si>
     <t>reportTypeDropdown</t>
   </si>
   <si>
-    <t>report_type_select</t>
+    <t>.product_sort_container select</t>
   </si>
   <si>
     <t>reportTable</t>
   </si>
   <si>
-    <t>table.reports-table</t>
-  </si>
-  <si>
-    <t>ConfirmationModal</t>
-  </si>
-  <si>
-    <t>confirmButton</t>
-  </si>
-  <si>
-    <t>//button[text()='Confirm']</t>
-  </si>
-  <si>
-    <t>#confirmModal</t>
-  </si>
-  <si>
-    <t>modalMessage</t>
-  </si>
-  <si>
-    <t>.modal-body-text</t>
+    <t>.inventory_list</t>
   </si>
 </sst>
 </file>
@@ -516,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -583,7 +550,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>10000</v>
@@ -600,13 +567,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
         <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
       </c>
       <c r="E4">
         <v>10000</v>
@@ -623,16 +590,16 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
       <c r="E5">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -643,19 +610,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
       <c r="E6">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -666,19 +633,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
       <c r="E7">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -689,16 +656,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8">
         <v>10000</v>
@@ -712,16 +679,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E9">
         <v>10000</v>
@@ -735,93 +702,24 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E10">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11">
-        <v>15000</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12">
-        <v>10000</v>
-      </c>
-      <c r="F12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13">
-        <v>10000</v>
-      </c>
-      <c r="F13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data/locators.xlsx
+++ b/data/locators.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="49">
   <si>
     <t>PageName</t>
   </si>
@@ -98,6 +98,66 @@
   </si>
   <si>
     <t>.inventory_list</t>
+  </si>
+  <si>
+    <t>productItem</t>
+  </si>
+  <si>
+    <t>.inventory_item:first-child</t>
+  </si>
+  <si>
+    <t>addToCartBtn</t>
+  </si>
+  <si>
+    <t>.inventory_item:first-child .btn_inventory</t>
+  </si>
+  <si>
+    <t>cartLink</t>
+  </si>
+  <si>
+    <t>shopping_cart_container</t>
+  </si>
+  <si>
+    <t>CartPage</t>
+  </si>
+  <si>
+    <t>checkoutBtn</t>
+  </si>
+  <si>
+    <t>checkout</t>
+  </si>
+  <si>
+    <t>CheckoutPage</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>first-name</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>last-name</t>
+  </si>
+  <si>
+    <t>postalCode</t>
+  </si>
+  <si>
+    <t>postal-code</t>
+  </si>
+  <si>
+    <t>continueBtn</t>
+  </si>
+  <si>
+    <t>continue</t>
+  </si>
+  <si>
+    <t>finishBtn</t>
+  </si>
+  <si>
+    <t>finish</t>
   </si>
 </sst>
 </file>
@@ -483,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -723,8 +783,836 @@
         <v>11</v>
       </c>
     </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11">
+        <v>10000</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12">
+        <v>10000</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13">
+        <v>10000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14">
+        <v>10000</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15">
+        <v>10000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16">
+        <v>10000</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17">
+        <v>10000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18">
+        <v>10000</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19">
+        <v>10000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20">
+        <v>10000</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21">
+        <v>10000</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22">
+        <v>10000</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23">
+        <v>10000</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24">
+        <v>10000</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25">
+        <v>10000</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26">
+        <v>10000</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27">
+        <v>10000</v>
+      </c>
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28">
+        <v>10000</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29">
+        <v>10000</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30">
+        <v>10000</v>
+      </c>
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31">
+        <v>10000</v>
+      </c>
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32">
+        <v>5000</v>
+      </c>
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33">
+        <v>15000</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34">
+        <v>10000</v>
+      </c>
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35">
+        <v>10000</v>
+      </c>
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36">
+        <v>10000</v>
+      </c>
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37">
+        <v>15000</v>
+      </c>
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38">
+        <v>10000</v>
+      </c>
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39">
+        <v>10000</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40">
+        <v>10000</v>
+      </c>
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41">
+        <v>10000</v>
+      </c>
+      <c r="F41" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42">
+        <v>10000</v>
+      </c>
+      <c r="F42" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43">
+        <v>10000</v>
+      </c>
+      <c r="F43" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44">
+        <v>10000</v>
+      </c>
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45">
+        <v>10000</v>
+      </c>
+      <c r="F45" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E46">
+        <v>10000</v>
+      </c>
+      <c r="F46" t="s">
+        <v>11</v>
+      </c>
+      <c r="G46" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>